--- a/scripts/test_sire_por_grado.xlsx
+++ b/scripts/test_sire_por_grado.xlsx
@@ -15098,7 +15098,7 @@
         <v>PÉREZ SARCEÑO, YARETZY GALILEA</v>
       </c>
       <c r="E115" t="str">
-        <v>Secci��n A</v>
+        <v>A</v>
       </c>
       <c r="F115" t="str">
         <v>Perito Contador</v>
